--- a/data/trans_dic/P1803_2016_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1803_2016_2023-Provincia-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 11,18</t>
+          <t>4,69; 10,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,42; 18,95</t>
+          <t>10,32; 17,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,74; 15,48</t>
+          <t>8,21; 16,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,84; 25,82</t>
+          <t>16,56; 24,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 12,2</t>
+          <t>7,31; 12,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,99; 20,8</t>
+          <t>14,06; 19,51</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,86</t>
+          <t>1,02; 3,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,19</t>
+          <t>3,59; 8,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,48</t>
+          <t>1,47; 4,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,89</t>
+          <t>6,25; 11,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,65</t>
+          <t>1,59; 3,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,27</t>
+          <t>5,44; 9,15</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,95</t>
+          <t>0,56; 3,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 14,03</t>
+          <t>7,47; 14,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,19</t>
+          <t>0,91; 4,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 15,35</t>
+          <t>9,18; 15,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,19</t>
+          <t>1,02; 3,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 13,88</t>
+          <t>9,09; 13,44</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 10,91</t>
+          <t>5,02; 10,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 15,51</t>
+          <t>6,72; 14,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,17</t>
+          <t>4,55; 10,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 12,61</t>
+          <t>9,02; 14,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,45</t>
+          <t>5,31; 9,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 12,28</t>
+          <t>8,54; 13,11</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,68</t>
+          <t>0,78; 4,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,96</t>
+          <t>1,64; 7,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 7,29</t>
+          <t>1,8; 7,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,33</t>
+          <t>1,61; 5,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,13</t>
+          <t>1,66; 4,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,76</t>
+          <t>2,06; 5,16</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,79; 11,34</t>
+          <t>4,58; 11,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,7; 12,47</t>
+          <t>5,62; 12,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,51</t>
+          <t>2,23; 7,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,59; 17,12</t>
+          <t>10,49; 17,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 8,51</t>
+          <t>4,17; 8,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,94; 13,31</t>
+          <t>8,68; 13,11</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,28</t>
+          <t>3,54; 7,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,89; 16,37</t>
+          <t>10,08; 15,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,84</t>
+          <t>4,06; 7,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,38; 15,94</t>
+          <t>12,17; 16,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,7</t>
+          <t>4,14; 6,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,53; 14,81</t>
+          <t>11,85; 15,5</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,51</t>
+          <t>2,68; 5,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,94; 68,11</t>
+          <t>1,41; 3,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,72</t>
+          <t>4,96; 8,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,5</t>
+          <t>1,67; 3,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,57</t>
+          <t>4,31; 6,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,03; 48,09</t>
+          <t>1,67; 3,15</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,33</t>
+          <t>3,9; 5,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,04; 33,89</t>
+          <t>7,07; 9,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,37</t>
+          <t>4,79; 6,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,73; 10,6</t>
+          <t>9,03; 10,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,5; 5,62</t>
+          <t>4,54; 5,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,7; 23,36</t>
+          <t>8,4; 9,69</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44551</t>
+          <t>43214</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61844</t>
+          <t>62455</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>106395</t>
+          <t>105668</t>
         </is>
       </c>
     </row>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14387; 32839</t>
+          <t>13767; 32050</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32450; 59015</t>
+          <t>32892; 55867</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22351; 44689</t>
+          <t>23704; 46307</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51659; 74792</t>
+          <t>52332; 75905</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42354; 71069</t>
+          <t>42590; 72046</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90090; 125051</t>
+          <t>89298; 123882</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30831</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>44828</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74024</t>
+          <t>75015</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5259; 19396</t>
+          <t>5135; 18811</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17913; 47621</t>
+          <t>19071; 47240</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7615; 23445</t>
+          <t>7710; 24311</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32682; 55926</t>
+          <t>34080; 60133</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15807; 37413</t>
+          <t>16350; 36372</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56602; 95682</t>
+          <t>58494; 98417</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>32744</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42408</t>
+          <t>42508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75792</t>
+          <t>75252</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1824; 12576</t>
+          <t>1796; 10785</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23912; 44341</t>
+          <t>23610; 45405</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3160; 14079</t>
+          <t>3074; 13964</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32859; 53530</t>
+          <t>32655; 53817</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6674; 20899</t>
+          <t>6669; 21935</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61907; 92247</t>
+          <t>61045; 90268</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>34221</t>
+          <t>36289</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43413</t>
+          <t>47932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77634</t>
+          <t>84221</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18950; 40364</t>
+          <t>18581; 40565</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23196; 48484</t>
+          <t>25058; 52663</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16959; 39389</t>
+          <t>17620; 39079</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26308; 59997</t>
+          <t>38045; 60980</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41836; 71575</t>
+          <t>40193; 70144</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53215; 96781</t>
+          <t>67883; 104245</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>14173</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1648; 9886</t>
+          <t>1642; 9411</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3593; 14227</t>
+          <t>3372; 14952</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3934; 15926</t>
+          <t>3925; 16245</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3369; 11116</t>
+          <t>3656; 12065</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7261; 22053</t>
+          <t>7119; 20984</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8320; 22332</t>
+          <t>8915; 22347</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>22594</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34748</t>
+          <t>35829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57940</t>
+          <t>58423</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12600; 29835</t>
+          <t>12062; 29080</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15376; 33612</t>
+          <t>15212; 32505</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7085; 20511</t>
+          <t>6078; 20225</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27215; 44014</t>
+          <t>27676; 45359</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22378; 45617</t>
+          <t>22340; 45036</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47079; 70102</t>
+          <t>46398; 70083</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>80839</t>
+          <t>90905</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>97396</t>
+          <t>110666</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>178234</t>
+          <t>201570</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23091; 47790</t>
+          <t>23219; 47311</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>61764; 102192</t>
+          <t>72537; 114562</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27970; 54196</t>
+          <t>28070; 54155</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45655; 135414</t>
+          <t>93933; 128789</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>55938; 90265</t>
+          <t>55745; 92768</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>111010; 218226</t>
+          <t>176805; 231251</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>260140</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>276882</t>
+          <t>38480</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20633; 42908</t>
+          <t>20890; 43333</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>18046; 632568</t>
+          <t>11286; 30652</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>40713; 72006</t>
+          <t>41004; 69936</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11422; 25144</t>
+          <t>13910; 28616</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>68701; 105388</t>
+          <t>69115; 106905</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33448; 791727</t>
+          <t>27130; 51344</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>514507</t>
+          <t>281996</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>345891</t>
+          <t>370807</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>860399</t>
+          <t>652803</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>130818; 180874</t>
+          <t>132226; 181067</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>278006; 1172526</t>
+          <t>249779; 322394</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>166982; 225840</t>
+          <t>169707; 223109</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>283016; 387944</t>
+          <t>337119; 401514</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>312431; 390129</t>
+          <t>315049; 391061</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>619385; 1663521</t>
+          <t>610512; 704185</t>
         </is>
       </c>
     </row>
